--- a/templates/Phase3_Trust_Surface_Register.xlsx
+++ b/templates/Phase3_Trust_Surface_Register.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Surface Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Chains" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification Guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trust Surface Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Trust Chains" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Verification Guide" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,29 +28,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00F57F17"/>
+      <color rgb="FFF57F17"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,12 +58,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F57F17"/>
+        <fgColor rgb="FFF57F17"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,38 +82,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,73 +484,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00F57F17"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OSRA PHASE 3 — TRUST SURFACE REGISTER (v1.1)</t>
+          <t>OSRA PHASE 3 — TRUST SURFACE REGISTER (v1.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Link every signal to the Phase 1 dependency ID(s) it concerns (comma-separated). Phase 4 reads trust gaps per dependency through that link. Trust Gap is Y when a decision depends on the signal and it is Unverified or Unverifiable, or verified with Scope Match = N. Yellow = input, purple = formula.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Signal ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dependency ID(s)
+(from Phase 1)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Trust Signal
 Category</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Specific Trust Signal</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>What Decision/Claim
 Depends On It</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Verification
 Status</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Verification
 Method</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Last
 Verified</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Scope
 Match? (Y/N/Partial)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Trust Gap?</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Consequence If
 Trust Signal Is False</t>
@@ -546,361 +583,1117 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TS-01</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>DEP-21</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Vendor performance</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>"99.95% uptime" — cloud SLA</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Business continuity assumption</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="6">
+        <f>IF(F4="","",IF(AND(E4&lt;&gt;"",OR(F4="Unverified",F4="Unverifiable",I4="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TS-02</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>DEP-01</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Vendor performance</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Model accuracy benchmark scores</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Decision to deploy model in production</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="6">
+        <f>IF(F5="","",IF(AND(E5&lt;&gt;"",OR(F5="Unverified",F5="Unverifiable",I5="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TS-03</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>DEP-10</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Vendor performance</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>"Enterprise-grade security"</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Risk assessment conclusion</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="6">
+        <f>IF(F6="","",IF(AND(E6&lt;&gt;"",OR(F6="Unverified",F6="Unverifiable",I6="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TS-04</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>DEP-10</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Vendor ISO 27001 certificate</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Third-party risk assessment</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="6">
+        <f>IF(F7="","",IF(AND(E7&lt;&gt;"",OR(F7="Unverified",F7="Unverifiable",I7="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TS-05</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>DEP-10</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Vendor SOC 2 Type II report</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Compliance evidence for regulators</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6">
+        <f>IF(F8="","",IF(AND(E8&lt;&gt;"",OR(F8="Unverified",F8="Unverifiable",I8="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TS-06</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>DEP-22</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Model deprecation notice period</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Migration planning assumption</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="6">
+        <f>IF(F9="","",IF(AND(E9&lt;&gt;"",OR(F9="Unverified",F9="Unverifiable",I9="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TS-07</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>DEP-23</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>SLA</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Data provider response time guarantee</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Real-time processing assumption</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="6">
+        <f>IF(F10="","",IF(AND(E10&lt;&gt;"",OR(F10="Unverified",F10="Unverifiable",I10="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TS-08</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>DEP-01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Internal testing</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Bias testing results</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>AI Act compliance claim</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="6">
+        <f>IF(F11="","",IF(AND(E11&lt;&gt;"",OR(F11="Unverified",F11="Unverifiable",I11="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TS-09</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>DEP-15</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Internal testing</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Penetration test scope</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Security posture claim</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="6">
+        <f>IF(F12="","",IF(AND(E12&lt;&gt;"",OR(F12="Unverified",F12="Unverifiable",I12="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TS-10</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Governance docs</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Risk assessment completeness</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Board-level risk reporting</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="6">
+        <f>IF(F13="","",IF(AND(E13&lt;&gt;"",OR(F13="Unverified",F13="Unverifiable",I13="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TS-11</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Governance docs</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Board AI risk report metrics</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Board duty of care / NED liability</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="6">
+        <f>IF(F14="","",IF(AND(E14&lt;&gt;"",OR(F14="Unverified",F14="Unverifiable",I14="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TS-12</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>DEP-10</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Implicit trust</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>"We use [major cloud], so security is handled"</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Shared responsibility assumption</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="6">
+        <f>IF(F15="","",IF(AND(E15&lt;&gt;"",OR(F15="Unverified",F15="Unverifiable",I15="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TS-13</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>DEP-01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Implicit trust</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>"It's [top model], so quality is guaranteed"</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Output quality assumption</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="6">
+        <f>IF(F16="","",IF(AND(E16&lt;&gt;"",OR(F16="Unverified",F16="Unverifiable",I16="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TS-14</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>DEP-09</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Human-in-the-loop</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>"A physician/analyst reviews every AI recommendation"</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>AI Act Art. 14 compliance (human oversight)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="6">
+        <f>IF(F17="","",IF(AND(E17&lt;&gt;"",OR(F17="Unverified",F17="Unverifiable",I17="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TS-15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>DEP-09</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Human-in-the-loop</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>"Operators can override the system at any time"</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Risk assessment: AI decisions are supervised</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="6">
+        <f>IF(F18="","",IF(AND(E18&lt;&gt;"",OR(F18="Unverified",F18="Unverifiable",I18="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TS-16</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>DEP-09</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Human-in-the-loop</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>"Final decision always rests with a human"</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Board assurance that AI is not autonomous</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="6">
+        <f>IF(F19="","",IF(AND(E19&lt;&gt;"",OR(F19="Unverified",F19="Unverifiable",I19="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TS-17</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>DEP-06</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Agent and tool delegation</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>"The agent can only call the tools it is permitted to call"</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Risk assessment: agent actions are bounded</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="6">
+        <f>IF(F20="","",IF(AND(E20&lt;&gt;"",OR(F20="Unverified",F20="Unverifiable",I20="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TS-18</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>DEP-07</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Agent and tool delegation</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>"The MCP server does what its tool description says"</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Decision to connect the server to the agent</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="6">
+        <f>IF(F21="","",IF(AND(E21&lt;&gt;"",OR(F21="Unverified",F21="Unverifiable",I21="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TS-19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>DEP-08</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Agent and tool delegation</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>"Tool credentials are scoped to one client or tenant"</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Client contract and data protection assurances</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="6">
+        <f>IF(F22="","",IF(AND(E22&lt;&gt;"",OR(F22="Unverified",F22="Unverifiable",I22="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TS-20</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="6">
+        <f>IF(F23="","",IF(AND(E23&lt;&gt;"",OR(F23="Unverified",F23="Unverifiable",I23="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TS-21</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="6">
+        <f>IF(F24="","",IF(AND(E24&lt;&gt;"",OR(F24="Unverified",F24="Unverifiable",I24="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TS-22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="6">
+        <f>IF(F25="","",IF(AND(E25&lt;&gt;"",OR(F25="Unverified",F25="Unverifiable",I25="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TS-23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="6">
+        <f>IF(F26="","",IF(AND(E26&lt;&gt;"",OR(F26="Unverified",F26="Unverifiable",I26="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TS-24</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="6">
+        <f>IF(F27="","",IF(AND(E27&lt;&gt;"",OR(F27="Unverified",F27="Unverifiable",I27="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TS-25</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="6">
+        <f>IF(F28="","",IF(AND(E28&lt;&gt;"",OR(F28="Unverified",F28="Unverifiable",I28="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TS-26</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="6">
+        <f>IF(F29="","",IF(AND(E29&lt;&gt;"",OR(F29="Unverified",F29="Unverifiable",I29="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TS-27</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="6">
+        <f>IF(F30="","",IF(AND(E30&lt;&gt;"",OR(F30="Unverified",F30="Unverifiable",I30="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TS-28</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="6">
+        <f>IF(F31="","",IF(AND(E31&lt;&gt;"",OR(F31="Unverified",F31="Unverifiable",I31="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TS-29</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="6">
+        <f>IF(F32="","",IF(AND(E32&lt;&gt;"",OR(F32="Unverified",F32="Unverifiable",I32="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TS-30</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="6">
+        <f>IF(F33="","",IF(AND(E33&lt;&gt;"",OR(F33="Unverified",F33="Unverifiable",I33="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TS-31</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="6">
+        <f>IF(F34="","",IF(AND(E34&lt;&gt;"",OR(F34="Unverified",F34="Unverifiable",I34="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TS-32</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="6">
+        <f>IF(F35="","",IF(AND(E35&lt;&gt;"",OR(F35="Unverified",F35="Unverifiable",I35="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TS-33</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="6">
+        <f>IF(F36="","",IF(AND(E36&lt;&gt;"",OR(F36="Unverified",F36="Unverifiable",I36="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TS-34</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="6">
+        <f>IF(F37="","",IF(AND(E37&lt;&gt;"",OR(F37="Unverified",F37="Unverifiable",I37="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TS-35</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="6">
+        <f>IF(F38="","",IF(AND(E38&lt;&gt;"",OR(F38="Unverified",F38="Unverifiable",I38="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TS-36</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="6">
+        <f>IF(F39="","",IF(AND(E39&lt;&gt;"",OR(F39="Unverified",F39="Unverifiable",I39="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TS-37</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="6">
+        <f>IF(F40="","",IF(AND(E40&lt;&gt;"",OR(F40="Unverified",F40="Unverifiable",I40="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TS-38</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="6">
+        <f>IF(F41="","",IF(AND(E41&lt;&gt;"",OR(F41="Unverified",F41="Unverifiable",I41="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>TS-39</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="6">
+        <f>IF(F42="","",IF(AND(E42&lt;&gt;"",OR(F42="Unverified",F42="Unverifiable",I42="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>TS-40</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="6">
+        <f>IF(F43="","",IF(AND(E43&lt;&gt;"",OR(F43="Unverified",F43="Unverifiable",I43="N")),"Y","N"))</f>
+        <v/>
+      </c>
+      <c r="K43" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="C4:C43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="OSRA" error="Choose a value from the list." type="list">
+      <formula1>"Vendor performance,Certification,SLA,Internal testing,Governance docs,Third-party assessment,Implicit trust,Human-in-the-loop,Agent and tool delegation"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="OSRA" error="Choose a value from the list." type="list">
+      <formula1>"Verified,Partially Verified,Unverified,Unverifiable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I4:I43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="OSRA" error="Choose a value from the list." type="list">
+      <formula1>"Y,N,Partial"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -908,52 +1701,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFB300"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Signal ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Your Organisation
 Trusts...</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Vendor A
 (Direct Provider)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Vendor A Trusts...
 (Tier 2)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Tier 2 Trusts...
 (Tier 3)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Chain Depth</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Verified At
 Each Level? (Y/N)</t>
@@ -961,154 +1759,325 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>TS-01</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>E.g. Azure OpenAI uptime</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Microsoft Azure</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>OpenAI model availability</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>OpenAI's cloud infra</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr"/>
+      <c r="F2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>TS-02</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>E.g. Data enrichment quality</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Refinitiv</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Refinitiv's data sources</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Data enrichment vendor</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Vendor's data sources</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Original data providers</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
+      <c r="F3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TS-14</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>E.g. Human oversight effective</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Internal operations</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Analyst training adequacy</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Workload allows review time</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="F4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TS-18</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>E.g. MCP server behaves as described</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Community maintainer</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Public package registry</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Server's transitive dependencies</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr"/>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Chain depth feeds the Trust Depth factor in Phase 4 (1 = verified by the organisation or internal and monitored; 2 = one external party; 3 = two layers; 4 = three or more layers, none verified; 5 = the chain is opaque).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:G27"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="OSRA" error="Choose a value from the list." type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1116,74 +2085,85 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFF176"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Independently tested/audited by the organisation or a commissioned third party. Evidence on file.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Partially Verified</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Some aspect verified but scope does not fully match the trust signal. E.g. ISO cert covers process, not performance.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>The organisation accepts this claim at face value. No independent verification performed.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Unverifiable</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>The claim cannot be independently verified due to vendor opacity, proprietary systems, or contractual restrictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Trust gap (v1.2)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>A decision, compliance claim or risk assessment depends on the signal, AND the signal is Unverified or Unverifiable, or its verification does not cover the claim relied on (Scope Match = N). A trust gap on a dependency meets condition 3 in Phase 4.</t>
         </is>
       </c>
     </row>
